--- a/M2_Statistica_&_Excel/W1_D1.xlsx
+++ b/M2_Statistica_&_Excel/W1_D1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SZN\Desktop\EPICODE CORSO\esercizi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9DE59F-26D4-435A-8DCC-DFFC7EC53CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7DEFCD-4ED2-4852-9ABB-6BD820B5DDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CE56E516-1B62-4124-9771-D4FC9EA234F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CE56E516-1B62-4124-9771-D4FC9EA234F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Esercizio 1" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,6 @@
     <definedName name="_18_21">'Esercizio 1'!$C$17:$D$17</definedName>
     <definedName name="_22_25">'Esercizio 1'!$C$18:$D$18</definedName>
     <definedName name="_26_30">'Esercizio 1'!$C$19:$D$19</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">'Esercizio 1'!$B$1</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Esercizio 1'!$B$2:$B$13</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'Esercizio 2'!$B$1</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Esercizio 2'!$B$2:$B$14</definedName>
     <definedName name="classe">'Esercizio 2'!$A$19:$A$21</definedName>
     <definedName name="classi">'Esercizio 1'!$C$17:$D$19</definedName>
     <definedName name="f">'Esercizio 1'!$D$17:$D$19</definedName>
@@ -61,7 +57,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -83,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
   <si>
     <t>studenti</t>
   </si>
@@ -130,21 +126,6 @@
     <t>MEDIA</t>
   </si>
   <si>
-    <t>LIMITE_INFERIORE (limiti Tukey)</t>
-  </si>
-  <si>
-    <t>LIMITE_SUPERIORE (limiti Tukey)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INFERIORE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPERIORE </t>
-  </si>
-  <si>
-    <t>limiti di Tukey</t>
-  </si>
-  <si>
     <t>classe</t>
   </si>
   <si>
@@ -188,6 +169,21 @@
   </si>
   <si>
     <t>NO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMITE SUPERIORE </t>
+  </si>
+  <si>
+    <t>LIMITE INFERIORE</t>
+  </si>
+  <si>
+    <t>Analisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMITE INFERIORE </t>
+  </si>
+  <si>
+    <t>LIMITE SUPERIORE</t>
   </si>
 </sst>
 </file>
@@ -250,7 +246,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -273,12 +269,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -298,9 +307,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -313,10 +319,10 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2813,10 +2819,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3141,19 +3143,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="5">
-        <f>AVERAGE(voti)</f>
-        <v>26.666666666666668</v>
-      </c>
+      <c r="C1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
@@ -3162,12 +3161,12 @@
       <c r="B2" s="6">
         <v>18</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>13</v>
+      <c r="C2" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="D2" s="5">
-        <f>MEDIAN(voti)</f>
-        <v>28</v>
+        <f>AVERAGE(voti)</f>
+        <v>26.666666666666668</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -3177,11 +3176,11 @@
       <c r="B3" s="6">
         <v>22</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>12</v>
+      <c r="C3" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="D3" s="5">
-        <f>_xlfn.MODE.SNGL(voti)</f>
+        <f>MEDIAN(voti)</f>
         <v>28</v>
       </c>
     </row>
@@ -3192,8 +3191,13 @@
       <c r="B4" s="6">
         <v>25</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="5">
+        <f>_xlfn.MODE.SNGL(voti)</f>
+        <v>28</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
@@ -3202,7 +3206,7 @@
       <c r="B5" s="6">
         <v>25</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="5">
@@ -3217,10 +3221,10 @@
       <c r="B6" s="6">
         <v>27</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <f>_xlfn.STDEV.P(voti)</f>
         <v>3.496029493900505</v>
       </c>
@@ -3232,7 +3236,7 @@
       <c r="B7" s="6">
         <v>28</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="5">
@@ -3247,7 +3251,7 @@
       <c r="B8" s="6">
         <v>28</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="5">
@@ -3262,7 +3266,7 @@
       <c r="B9" s="6">
         <v>28</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="5">
@@ -3277,10 +3281,10 @@
       <c r="B10" s="6">
         <v>29</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="5">
         <f>(D7-(1.5*D9))</f>
         <v>18.625</v>
       </c>
@@ -3292,10 +3296,10 @@
       <c r="B11" s="6">
         <v>30</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="C11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="5">
         <f>(D8+(1.5*D9))</f>
         <v>35.625</v>
       </c>
@@ -3307,11 +3311,11 @@
       <c r="B12" s="6">
         <v>30</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>32</v>
+      <c r="C12" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -3323,17 +3327,17 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>31</v>
+      <c r="B16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -3347,7 +3351,7 @@
         <f>COUNTIFS(voti,"&gt;=18",voti,"&lt;21")</f>
         <v>1</v>
       </c>
-      <c r="D17" s="11" cm="1">
+      <c r="D17" s="10" cm="1">
         <f t="array" ref="D17:D19">_xlfn.TAKE(FREQUENCY(voti,B17:B19),3)/COUNT(voti)</f>
         <v>8.3333333333333329E-2</v>
       </c>
@@ -3363,7 +3367,7 @@
         <f>COUNTIFS(voti,"&gt;=22",voti,"&lt;26")</f>
         <v>3</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <v>0.25</v>
       </c>
     </row>
@@ -3378,7 +3382,7 @@
         <f>COUNTIFS(voti,"&gt;=26",voti,"&lt;31")</f>
         <v>8</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <v>0.66666666666666663</v>
       </c>
     </row>
@@ -3390,10 +3394,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D22" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:D1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3410,207 +3417,203 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="12"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6">
+        <v>18</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="7">
+      <c r="D2" s="5">
         <f>AVERAGE(voti)</f>
         <v>31.923076923076923</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12">
-        <v>18</v>
-      </c>
-      <c r="C2" s="10" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6">
+        <v>22</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D3" s="5">
         <f>MEDIAN(voti)</f>
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12">
-        <v>22</v>
-      </c>
-      <c r="C3" s="10" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6">
         <v>25</v>
       </c>
-      <c r="D3" s="7">
+      <c r="C4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="5">
         <f>_xlfn.VAR.P(voti)</f>
         <v>342.84023668639054</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
-        <v>3</v>
-      </c>
-      <c r="B4" s="12">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6">
         <v>25</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="7">
+      <c r="C5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="5">
         <f>_xlfn.STDEV.P(voti)</f>
         <v>18.515945471036325</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
-        <v>4</v>
-      </c>
-      <c r="B5" s="12">
-        <v>25</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="7"/>
-    </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="6">
         <v>27</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <f>_xlfn.QUARTILE.INC(voti,1)</f>
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="6">
         <v>28</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <f>_xlfn.QUARTILE.INC(voti,3)</f>
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="6">
         <v>28</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <f>Q3_-Q1_</f>
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>28</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="7"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
-        <v>9</v>
-      </c>
-      <c r="B10" s="12">
-        <v>29</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="7"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12">
-        <v>30</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="C9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="5">
         <f>(Q1_-(1.5*IQR))</f>
         <v>17.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="12">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6">
+        <v>29</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="D10" s="5">
         <f>(Q3_+(1.5*IQR))</f>
         <v>37.5</v>
       </c>
     </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6">
+        <v>30</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6">
+        <v>30</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="6">
         <v>30</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="7">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6">
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="13">
-        <v>13</v>
-      </c>
-      <c r="B14" s="13">
-        <v>95</v>
-      </c>
-      <c r="C14" s="2"/>
-    </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="9" t="s">
+      <c r="A18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>28</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -3624,7 +3627,7 @@
         <f t="array" ref="C19:C21">_xlfn.TAKE(FREQUENCY(voti,B19:B21),3)</f>
         <v>1</v>
       </c>
-      <c r="D19" s="11" cm="1">
+      <c r="D19" s="10" cm="1">
         <f t="array" ref="D19:D21">_xlfn.TAKE(FREQUENCY(voti,B19:B21),3)/COUNT(voti)</f>
         <v>7.6923076923076927E-2</v>
       </c>
@@ -3639,13 +3642,13 @@
       <c r="C20" s="5">
         <v>3</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="10">
         <v>0.23076923076923078</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B21" s="5">
         <v>95</v>
@@ -3653,22 +3656,25 @@
       <c r="C21" s="5">
         <v>9</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <v>0.69230769230769229</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D24" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:D1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/M2_Statistica_&_Excel/W1_D1.xlsx
+++ b/M2_Statistica_&_Excel/W1_D1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SZN\Desktop\EPICODE CORSO\esercizi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SZN\Desktop\EPICODE CORSO\esercizi\esercizi consegnati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7DEFCD-4ED2-4852-9ABB-6BD820B5DDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5D961D-2900-4996-BC1A-B6F14C63768E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CE56E516-1B62-4124-9771-D4FC9EA234F2}"/>
   </bookViews>
